--- a/Modul Quantitative Methoden II_Termine.xlsx
+++ b/Modul Quantitative Methoden II_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stephangoerigk/Desktop/Universität/CFH/Lehre/Bachelor/Quantitative Methoden II/VO_Statistik II/Statistik_II_Folien/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicosteffen/Documents/01 Arbeit/01 CFH/01 Stephan Goerigk/R/Github Repositories/QMII/Statistik_II_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78108A3-5384-5D4A-A798-1552E1B559CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A18B39C-C33B-E349-A9CB-F67842717185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-280" yWindow="1480" windowWidth="29400" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1480" windowWidth="29400" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Einheit</t>
   </si>
@@ -70,37 +70,49 @@
     <t>Robuste Tests</t>
   </si>
   <si>
-    <t xml:space="preserve">17.04.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.04.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.05.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.05.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.05.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.06.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.06.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.07.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.07.2025	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07.2025	</t>
+    <t xml:space="preserve">15.04.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.04.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.04.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.05.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.05.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.05.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.05.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.06.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.06.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.06.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.07.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.07.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.07.2026	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.07.2026	</t>
+  </si>
+  <si>
+    <t>Curriculare Reserve</t>
   </si>
 </sst>
 </file>
@@ -110,7 +122,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m\.yy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -129,19 +141,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -174,8 +173,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -394,7 +391,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="41.33203125" customWidth="1"/>
@@ -427,7 +424,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>4</v>
@@ -438,7 +435,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -504,7 +501,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
@@ -515,7 +512,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>12</v>
@@ -526,7 +523,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>13</v>
@@ -536,7 +533,9 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C13" s="4" t="s">
         <v>15</v>
       </c>
@@ -545,12 +544,26 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="C14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>